--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487884_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487884_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S. BARROS GARCIA</t>
+          <t>T. PIERRE PHILIPPE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.103</v>
+        <v>4.6715</v>
       </c>
       <c r="E2" t="n">
-        <v>5.0708</v>
+        <v>7.2538</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.9678</v>
+        <v>-2.5823</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8961</v>
+        <v>3.0159</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.015</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9111</v>
+        <v>2.4509</v>
       </c>
       <c r="J2" t="n">
-        <v>3.5497</v>
+        <v>8.008900000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>1.4303</v>
+        <v>4.1742</v>
       </c>
       <c r="L2" t="n">
-        <v>2.1194</v>
+        <v>3.8347</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.6536</v>
+        <v>-4.993</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.4453</v>
+        <v>-3.6092</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.2083</v>
+        <v>-1.3838</v>
       </c>
       <c r="P2" t="n">
-        <v>1.0406</v>
+        <v>1.4568</v>
       </c>
       <c r="Q2" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R2" t="n">
-        <v>2.0812</v>
+        <v>2.4974</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3986</v>
+        <v>-1.0749</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0033</v>
+        <v>-0.9881</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3953</v>
+        <v>-0.0867</v>
       </c>
       <c r="V2" t="n">
-        <v>2.565</v>
+        <v>1.2737</v>
       </c>
       <c r="W2" t="n">
-        <v>2.565</v>
+        <v>1.2737</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. TSEGAKELE</t>
+          <t>S. BARROS GARCIA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.65</v>
+        <v>4.2182</v>
       </c>
       <c r="E3" t="n">
-        <v>3.0718</v>
+        <v>4.9218</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5782</v>
+        <v>-0.7036</v>
       </c>
       <c r="G3" t="n">
-        <v>2.0654</v>
+        <v>0.8961</v>
       </c>
       <c r="H3" t="n">
-        <v>2.2663</v>
+        <v>-0.015</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2008</v>
+        <v>0.9111</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2984</v>
+        <v>3.5497</v>
       </c>
       <c r="K3" t="n">
-        <v>3.1808</v>
+        <v>1.4303</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1176</v>
+        <v>2.1194</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.2329</v>
+        <v>-2.6536</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9145</v>
+        <v>-1.4453</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3184</v>
+        <v>-1.2083</v>
       </c>
       <c r="P3" t="n">
-        <v>1.4568</v>
+        <v>1.0406</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4568</v>
+        <v>2.0812</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4815</v>
+        <v>-0.2835</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1272</v>
+        <v>-0.1524</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3543</v>
+        <v>-0.1311</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.3538</v>
+        <v>2.565</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.3538</v>
+        <v>2.565</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T. PIERRE PHILIPPE</t>
+          <t>A. TSEGAKELE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.5458</v>
+        <v>3.1001</v>
       </c>
       <c r="E4" t="n">
-        <v>6.4804</v>
+        <v>2.8156</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.9346</v>
+        <v>0.2846</v>
       </c>
       <c r="G4" t="n">
-        <v>3.0159</v>
+        <v>2.0654</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5649999999999999</v>
+        <v>2.2663</v>
       </c>
       <c r="I4" t="n">
-        <v>2.4509</v>
+        <v>-0.2008</v>
       </c>
       <c r="J4" t="n">
-        <v>8.008900000000001</v>
+        <v>3.2984</v>
       </c>
       <c r="K4" t="n">
-        <v>4.1742</v>
+        <v>3.1808</v>
       </c>
       <c r="L4" t="n">
-        <v>3.8347</v>
+        <v>0.1176</v>
       </c>
       <c r="M4" t="n">
-        <v>-4.993</v>
+        <v>-1.2329</v>
       </c>
       <c r="N4" t="n">
-        <v>-3.6092</v>
+        <v>-0.9145</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.3838</v>
+        <v>-0.3184</v>
       </c>
       <c r="P4" t="n">
         <v>1.4568</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.4974</v>
+        <v>1.4568</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.2006</v>
+        <v>-0.0683</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.7616</v>
+        <v>-0.129</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.439</v>
+        <v>0.0607</v>
       </c>
       <c r="V4" t="n">
-        <v>1.2737</v>
+        <v>-0.3538</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2737</v>
+        <v>-0.3538</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.6805</v>
+        <v>-1.0057</v>
       </c>
       <c r="E5" t="n">
-        <v>0.173</v>
+        <v>0.0239</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.8535</v>
+        <v>-1.0297</v>
       </c>
       <c r="G5" t="n">
         <v>-0.7994</v>
@@ -844,13 +844,13 @@
         <v>1.2487</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4945</v>
+        <v>0.1693</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3882</v>
+        <v>0.2391</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1064</v>
+        <v>-0.0698</v>
       </c>
       <c r="V5" t="n">
         <v>-0.5838</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.88</v>
+        <v>-1.7663</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.6363</v>
+        <v>-1.4639</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2437</v>
+        <v>-0.3024</v>
       </c>
       <c r="G6" t="n">
         <v>-1.9403</v>
@@ -922,13 +922,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1696</v>
+        <v>-0.056</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4567</v>
+        <v>-0.2843</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2871</v>
+        <v>0.2284</v>
       </c>
       <c r="V6" t="n">
         <v>0.23</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.8</v>
+        <v>-2.472</v>
       </c>
       <c r="E7" t="n">
-        <v>0.119</v>
+        <v>0.5057</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.919</v>
+        <v>-2.9777</v>
       </c>
       <c r="G7" t="n">
         <v>-1.8755</v>
@@ -1000,13 +1000,13 @@
         <v>1.2487</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.1326</v>
+        <v>-0.8046</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.5006</v>
+        <v>-1.1139</v>
       </c>
       <c r="U7" t="n">
-        <v>0.368</v>
+        <v>0.3093</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.0544</v>
+        <v>-2.766</v>
       </c>
       <c r="E8" t="n">
-        <v>1.0528</v>
+        <v>1.5467</v>
       </c>
       <c r="F8" t="n">
-        <v>-4.1072</v>
+        <v>-4.3127</v>
       </c>
       <c r="G8" t="n">
         <v>-1.3248</v>
@@ -1078,13 +1078,13 @@
         <v>1.2487</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6433</v>
+        <v>-0.3549</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.2396</v>
+        <v>-0.7458</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5964</v>
+        <v>0.3908</v>
       </c>
       <c r="V8" t="n">
         <v>-2.3351</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.5461</v>
+        <v>-3.185</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.823</v>
+        <v>-1.6087</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.7231</v>
+        <v>-1.5763</v>
       </c>
       <c r="G9" t="n">
         <v>-1.8734</v>
@@ -1156,13 +1156,13 @@
         <v>0.4162</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.0484</v>
+        <v>-0.6873</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7177</v>
+        <v>-0.5034</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3308</v>
+        <v>-0.184</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.6364</v>
+        <v>-3.5837</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.7738</v>
+        <v>-1.7504</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.8627</v>
+        <v>-1.8333</v>
       </c>
       <c r="G10" t="n">
         <v>-2.1432</v>
@@ -1234,13 +1234,13 @@
         <v>2.0812</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4495</v>
+        <v>-0.3968</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2643</v>
+        <v>-0.2409</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1852</v>
+        <v>-0.1559</v>
       </c>
       <c r="V10" t="n">
         <v>-1.0437</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.539</v>
+        <v>-8.3963</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.342</v>
+        <v>-5.1992</v>
       </c>
       <c r="F11" t="n">
         <v>-3.1971</v>
@@ -1312,10 +1312,10 @@
         <v>0.2081</v>
       </c>
       <c r="S11" t="n">
-        <v>0.7639</v>
+        <v>-0.09329999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5806</v>
+        <v>-0.2767</v>
       </c>
       <c r="U11" t="n">
         <v>0.1833</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-11.8376</v>
+        <v>-11.1852</v>
       </c>
       <c r="E12" t="n">
-        <v>6.3927</v>
+        <v>7.045299999999998</v>
       </c>
       <c r="F12" t="n">
         <v>-18.2305</v>
@@ -1390,19 +1390,19 @@
         <v>12.487</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.302700000000002</v>
+        <v>-3.6503</v>
       </c>
       <c r="T12" t="n">
-        <v>-4.847799999999999</v>
+        <v>-4.1954</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5452000000000001</v>
+        <v>0.545</v>
       </c>
       <c r="V12" t="n">
         <v>-1.1853</v>
       </c>
       <c r="W12" t="n">
-        <v>5.1124</v>
+        <v>5.112400000000001</v>
       </c>
       <c r="X12" t="n">
         <v>-6.297600000000001</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>11.0873</v>
+        <v>10.5207</v>
       </c>
       <c r="E13" t="n">
-        <v>9.496600000000001</v>
+        <v>9.282299999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5907</v>
+        <v>1.2384</v>
       </c>
       <c r="G13" t="n">
         <v>7.4851</v>
@@ -1468,13 +1468,13 @@
         <v>1.6649</v>
       </c>
       <c r="S13" t="n">
-        <v>1.5515</v>
+        <v>0.9848</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0867</v>
+        <v>-0.1276</v>
       </c>
       <c r="U13" t="n">
-        <v>1.4647</v>
+        <v>1.1124</v>
       </c>
       <c r="V13" t="n">
         <v>1.6345</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.5876</v>
+        <v>6.8298</v>
       </c>
       <c r="E14" t="n">
-        <v>6.5009</v>
+        <v>7.0367</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0867</v>
+        <v>-0.2069</v>
       </c>
       <c r="G14" t="n">
         <v>4.148</v>
@@ -1546,13 +1546,13 @@
         <v>1.6649</v>
       </c>
       <c r="S14" t="n">
-        <v>0.7458</v>
+        <v>0.9879</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7581</v>
+        <v>-0.2224</v>
       </c>
       <c r="U14" t="n">
-        <v>1.5039</v>
+        <v>1.2103</v>
       </c>
       <c r="V14" t="n">
         <v>0.237</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.7527</v>
+        <v>5.0257</v>
       </c>
       <c r="E15" t="n">
-        <v>4.4963</v>
+        <v>4.7106</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2564</v>
+        <v>0.3151</v>
       </c>
       <c r="G15" t="n">
         <v>2.107</v>
@@ -1624,13 +1624,13 @@
         <v>1.0406</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0548</v>
+        <v>0.3279</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.64</v>
+        <v>-0.4257</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6949</v>
+        <v>0.7536</v>
       </c>
       <c r="V15" t="n">
         <v>1.7584</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.2708</v>
+        <v>3.0962</v>
       </c>
       <c r="E16" t="n">
-        <v>3.8019</v>
+        <v>3.4804</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5311</v>
+        <v>-0.3843</v>
       </c>
       <c r="G16" t="n">
         <v>5.7343</v>
@@ -1702,13 +1702,13 @@
         <v>1.4568</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.3923</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2824</v>
+        <v>-0.039</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2845</v>
+        <v>0.4313</v>
       </c>
       <c r="V16" t="n">
         <v>-0.1168</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5869</v>
+        <v>-0.3535</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2113</v>
+        <v>0.5327</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7982</v>
+        <v>-0.8863</v>
       </c>
       <c r="G17" t="n">
         <v>0.3683</v>
@@ -1780,13 +1780,13 @@
         <v>1.2487</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4508</v>
+        <v>0.6842</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5748</v>
+        <v>-0.2533</v>
       </c>
       <c r="U17" t="n">
-        <v>1.0256</v>
+        <v>0.9376</v>
       </c>
       <c r="V17" t="n">
         <v>0.467</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. CORREIA</t>
+          <t>L. PAREJO CAMACHO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.6296</v>
+        <v>-2.2198</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2445</v>
+        <v>-2.5482</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.385</v>
+        <v>0.3284</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.7232</v>
+        <v>-2.3114</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.693</v>
+        <v>0.3158</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0302</v>
+        <v>-2.6273</v>
       </c>
       <c r="J19" t="n">
-        <v>0.265</v>
+        <v>-2.4705</v>
       </c>
       <c r="K19" t="n">
-        <v>0.2258</v>
+        <v>0.2303</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0392</v>
+        <v>-2.7007</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.9882</v>
+        <v>0.1591</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.9188</v>
+        <v>0.0856</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0694</v>
+        <v>0.0735</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.6244</v>
+        <v>0.2081</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0406</v>
+        <v>-0.2081</v>
       </c>
       <c r="R19" t="n">
         <v>0.4162</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5317</v>
+        <v>-0.1164</v>
       </c>
       <c r="T19" t="n">
-        <v>0.531</v>
+        <v>-0.09950000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0007</v>
+        <v>-0.0169</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.8137</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.8137</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L. PAREJO CAMACHO</t>
+          <t>S. CORREIA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.7277</v>
+        <v>-2.7264</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.7625</v>
+        <v>-0.4588</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0348</v>
+        <v>-2.2676</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.3114</v>
+        <v>-1.7232</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3158</v>
+        <v>-1.693</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.6273</v>
+        <v>-0.0302</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.4705</v>
+        <v>0.265</v>
       </c>
       <c r="K20" t="n">
-        <v>0.2303</v>
+        <v>0.2258</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.7007</v>
+        <v>0.0392</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1591</v>
+        <v>-1.9882</v>
       </c>
       <c r="N20" t="n">
-        <v>0.0856</v>
+        <v>-1.9188</v>
       </c>
       <c r="O20" t="n">
-        <v>0.0735</v>
+        <v>-0.0694</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2081</v>
+        <v>-0.6244</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.2081</v>
+        <v>-1.0406</v>
       </c>
       <c r="R20" t="n">
         <v>0.4162</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6244</v>
+        <v>0.4348</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3138</v>
+        <v>0.3167</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3105</v>
+        <v>0.1181</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.8137</v>
       </c>
       <c r="W20" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.23</v>
+        <v>-0.8137</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>G. FERNANDEZ DIAZ</t>
+          <t>A. HERRERA DOMINGUEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.4442</v>
+        <v>-3.2397</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.6237</v>
+        <v>-1.402</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.8206</v>
+        <v>-1.8377</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.282</v>
+        <v>-2.0669</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.966</v>
+        <v>-0.9999</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.316</v>
+        <v>-1.0671</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.7755</v>
+        <v>-1.332</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.8147</v>
+        <v>0.0576</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0392</v>
+        <v>-1.3896</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.5064</v>
+        <v>-0.7349</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.1513</v>
+        <v>-1.0574</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.3551</v>
+        <v>0.3225</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.0812</v>
+        <v>0.2081</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>0.2081</v>
       </c>
       <c r="S21" t="n">
-        <v>1.1489</v>
+        <v>0.3704</v>
       </c>
       <c r="T21" t="n">
-        <v>1.233</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0842</v>
+        <v>0.4404</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.23</v>
+        <v>-1.7513</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.23</v>
+        <v>-1.7513</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. HERRERA DOMINGUEZ</t>
+          <t>G. FERNANDEZ DIAZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.5905</v>
+        <v>-4.2134</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.7235</v>
+        <v>-2.4809</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.8671</v>
+        <v>-1.7325</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.0669</v>
+        <v>-2.282</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.9999</v>
+        <v>-1.966</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.0671</v>
+        <v>-0.316</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.332</v>
+        <v>-0.7755</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0576</v>
+        <v>-0.8147</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.3896</v>
+        <v>0.0392</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.7349</v>
+        <v>-1.5064</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.0574</v>
+        <v>-1.1513</v>
       </c>
       <c r="O22" t="n">
-        <v>0.3225</v>
+        <v>-0.3551</v>
       </c>
       <c r="P22" t="n">
-        <v>0.2081</v>
+        <v>-2.0812</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-2.0812</v>
       </c>
       <c r="R22" t="n">
-        <v>0.2081</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0196</v>
+        <v>0.3797</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3915</v>
+        <v>0.3758</v>
       </c>
       <c r="U22" t="n">
-        <v>0.411</v>
+        <v>0.0039</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.7513</v>
+        <v>-0.23</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.7513</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>11.8377</v>
+        <v>11.8378</v>
       </c>
       <c r="E23" t="n">
         <v>18.2304</v>
       </c>
       <c r="F23" t="n">
-        <v>-6.392799999999998</v>
+        <v>-6.392799999999999</v>
       </c>
       <c r="G23" t="n">
         <v>10.5121</v>
@@ -2218,7 +2218,7 @@
         <v>9.0832</v>
       </c>
       <c r="I23" t="n">
-        <v>1.4285</v>
+        <v>1.428499999999999</v>
       </c>
       <c r="J23" t="n">
         <v>24.965</v>
@@ -2227,13 +2227,13 @@
         <v>18.046</v>
       </c>
       <c r="L23" t="n">
-        <v>6.9192</v>
+        <v>6.919200000000001</v>
       </c>
       <c r="M23" t="n">
         <v>-14.453</v>
       </c>
       <c r="N23" t="n">
-        <v>-8.9626</v>
+        <v>-8.962600000000002</v>
       </c>
       <c r="O23" t="n">
         <v>-5.4904</v>
@@ -2248,13 +2248,13 @@
         <v>8.324499999999999</v>
       </c>
       <c r="S23" t="n">
-        <v>4.3028</v>
+        <v>4.3027</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5450999999999997</v>
+        <v>-0.545</v>
       </c>
       <c r="U23" t="n">
-        <v>4.8477</v>
+        <v>4.8478</v>
       </c>
       <c r="V23" t="n">
         <v>1.1851</v>
